--- a/ExtractorExcelToExcel/files_for_test/Data/Test_base.xlsx
+++ b/ExtractorExcelToExcel/files_for_test/Data/Test_base.xlsx
@@ -142,7 +142,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -175,7 +175,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -363,7 +363,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
